--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр Мариуполь на .xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/новый_бланк/Бланк заказов сыр Мариуполь на .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\новый_бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C71ACD2-E6F2-4D31-AE09-5C240D2D872E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8DB153-32D2-461F-AD15-FE5AF7338C7C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,12 +177,6 @@
     <t>Продукт белково-жировой Сметанковый 50% вес ТМ Коровино</t>
   </si>
   <si>
-    <t>Спред растительно-сливочный «Сливочный вкус» 82,5% 180гр</t>
-  </si>
-  <si>
-    <t>Спред растительно-сливочный «Сливочный вкус» 72,5% 180гр</t>
-  </si>
-  <si>
     <t>Сырный продукт Моцарелла 45% (батоны) 1,0кг ТМ "КОРОВИНО"</t>
   </si>
   <si>
@@ -262,13 +256,19 @@
   </si>
   <si>
     <t>Сыр копченый "Косичка" мини ПАПА МОЖЕТ 55г лоток</t>
+  </si>
+  <si>
+    <t>Майонез провансаль классический с массовой долей жира 67% ТМ «ПАПА МОЖЕТ» 186г дой-пак с дозатором</t>
+  </si>
+  <si>
+    <t>Майонез провансаль классический оливковый с массовой долей жира 67% ТМ «ПАПА МОЖЕТ» 186г дой-пак с дозатором</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -382,6 +382,12 @@
       <name val="Liberation Sans1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Cyr"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -436,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -505,6 +511,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -911,7 +920,7 @@
         <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="6" t="s">
@@ -984,7 +993,7 @@
         <v>8783323</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" s="31">
         <v>4</v>
@@ -1034,7 +1043,7 @@
         <v>8785235</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="13">
         <v>5</v>
@@ -1213,7 +1222,7 @@
         <v>8784931</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C14" s="25">
         <v>5</v>
@@ -1365,7 +1374,7 @@
         <v>8444170</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" s="13">
         <v>8</v>
@@ -1769,7 +1778,7 @@
         <v>8445160</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C36" s="13">
         <v>8</v>
@@ -1794,7 +1803,7 @@
         <v>8445177</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C37" s="13">
         <v>8</v>
@@ -1816,10 +1825,10 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38" s="13">
         <v>10</v>
@@ -1841,10 +1850,10 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C39" s="13">
         <v>4</v>
@@ -1863,15 +1872,15 @@
         <v>0</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="10" customFormat="1">
       <c r="A40" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C40" s="13">
         <v>10</v>
@@ -1893,10 +1902,10 @@
     </row>
     <row r="41" spans="1:9" s="10" customFormat="1" ht="11.25" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C41" s="13">
         <v>4</v>
@@ -1915,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="15" customFormat="1">
@@ -2024,13 +2033,13 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="11">
-        <v>4421584</v>
+        <v>9985949</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
@@ -2038,8 +2047,8 @@
         <f>D46/C46</f>
         <v>0</v>
       </c>
-      <c r="G46" s="12">
-        <v>0.18</v>
+      <c r="G46" s="32">
+        <v>1</v>
       </c>
       <c r="H46" s="8">
         <f>G46*D46</f>
@@ -2049,84 +2058,84 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="11">
-        <v>4421577</v>
+        <v>8786928</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C47" s="13">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="8">
-        <f>D47/C47</f>
+        <f>E47/6</f>
         <v>0</v>
       </c>
       <c r="G47" s="12">
-        <v>0.18</v>
+        <v>1.5</v>
       </c>
       <c r="H47" s="8">
-        <f>G47*D47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="8"/>
+        <f>E47</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="11">
-        <v>9985949</v>
+        <v>6948270</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C48" s="13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="8">
-        <f>D48/C48</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="32">
-        <v>1</v>
+        <f t="shared" ref="F48:F57" si="4">D48/C48</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0.372</v>
       </c>
       <c r="H48" s="8">
-        <f>G48*D48</f>
+        <f t="shared" ref="H48:H57" si="5">G48*D48</f>
         <v>0</v>
       </c>
       <c r="I48" s="8"/>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="11">
-        <v>8786928</v>
+        <v>6948287</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C49" s="13">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="8">
-        <f>E49/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G49" s="12">
-        <v>1.5</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H49" s="8">
-        <f>E49</f>
-        <v>0</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>53</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="8"/>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="11">
-        <v>6948270</v>
+        <v>6948256</v>
       </c>
       <c r="B50" s="27" t="s">
         <v>55</v>
@@ -2137,21 +2146,21 @@
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="8">
-        <f t="shared" ref="F50:F57" si="4">D50/C50</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G50" s="12">
         <v>0.372</v>
       </c>
       <c r="H50" s="8">
-        <f t="shared" ref="H50:H57" si="5">G50*D50</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I50" s="8"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="11">
-        <v>6948287</v>
+        <v>6948263</v>
       </c>
       <c r="B51" s="27" t="s">
         <v>56</v>
@@ -2176,7 +2185,7 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="11">
-        <v>6948256</v>
+        <v>6948249</v>
       </c>
       <c r="B52" s="27" t="s">
         <v>57</v>
@@ -2191,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="12">
-        <v>0.372</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="H52" s="8">
         <f t="shared" si="5"/>
@@ -2200,14 +2209,14 @@
       <c r="I52" s="8"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="11">
-        <v>6948263</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>58</v>
+      <c r="A53" s="26">
+        <v>2105201</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>73</v>
       </c>
       <c r="C53" s="13">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
@@ -2216,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="12">
-        <v>0.74399999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="8">
         <f t="shared" si="5"/>
@@ -2225,14 +2234,14 @@
       <c r="I53" s="8"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="11">
-        <v>6948249</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>59</v>
+      <c r="A54" s="26">
+        <v>2103201</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>74</v>
       </c>
       <c r="C54" s="13">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
@@ -2241,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12">
-        <v>0.82499999999999996</v>
+        <v>0.1</v>
       </c>
       <c r="H54" s="8">
         <f t="shared" si="5"/>
@@ -2251,7 +2260,7 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="26">
-        <v>2105201</v>
+        <v>1103201</v>
       </c>
       <c r="B55" s="30" t="s">
         <v>75</v>
@@ -2266,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12">
-        <v>0.1</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H55" s="8">
         <f t="shared" si="5"/>
@@ -2276,24 +2285,24 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="26">
-        <v>2103201</v>
+        <v>6948362</v>
       </c>
       <c r="B56" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C56" s="13">
-        <v>24</v>
-      </c>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="8">
+      <c r="C56" s="35">
+        <v>20</v>
+      </c>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G56" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="H56" s="8">
+      <c r="G56" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H56" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2301,24 +2310,24 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="26">
-        <v>1103201</v>
+        <v>6948508</v>
       </c>
       <c r="B57" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C57" s="13">
-        <v>24</v>
-      </c>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="8">
+      <c r="C57" s="35">
+        <v>20</v>
+      </c>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G57" s="12">
-        <v>5.5E-2</v>
-      </c>
-      <c r="H57" s="8">
+      <c r="G57" s="22">
+        <v>0.186</v>
+      </c>
+      <c r="H57" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
